--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -39,79 +39,115 @@
     <t>SeriesName</t>
   </si>
   <si>
-    <t>Harrys Race Series #1 2026</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
     <t>Current</t>
   </si>
   <si>
-    <t>Planned</t>
-  </si>
-  <si>
-    <t>Complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrys Race SX </t>
-  </si>
-  <si>
-    <t>Harrys Race SZ</t>
-  </si>
-  <si>
-    <t>Harrys Race SX</t>
-  </si>
-  <si>
-    <t>Stage Uno</t>
-  </si>
-  <si>
-    <t>Stage Dos</t>
-  </si>
-  <si>
-    <t>Stage Tres</t>
-  </si>
-  <si>
-    <t>Stage Quatro</t>
-  </si>
-  <si>
-    <t>Stage Cinco</t>
-  </si>
-  <si>
-    <t>Stage Seis</t>
-  </si>
-  <si>
     <t>America/Toronto</t>
   </si>
   <si>
     <t>Local TZ</t>
   </si>
   <si>
-    <t>5c474c9b-cc47-4f65-8d5c-5a206475988c</t>
-  </si>
-  <si>
-    <t>c92abe92-7e93-40e3-9500-378cd792639f</t>
-  </si>
-  <si>
-    <t>Mungia | Spain</t>
-  </si>
-  <si>
-    <t>Sunset Ride from Calvi | Corsica</t>
-  </si>
-  <si>
     <t>EventId</t>
   </si>
   <si>
-    <t>d257a5e4-3b0e-4f3e-b0a7-084ad404df3e</t>
-  </si>
-  <si>
-    <t>Stage X</t>
-  </si>
-  <si>
-    <t>b02d01d1-d21e-4095-8788-878691be5de9</t>
-  </si>
-  <si>
-    <t>a880966a-1325-4a1d-882a-ece2dcbf9244</t>
+    <t>Harrys TT Series #1 Fall 2026</t>
+  </si>
+  <si>
+    <t>Bagnara C. to Cannitello over Scilla - Calabria</t>
+  </si>
+  <si>
+    <t>Arta to Playa de Muro | Mallorca</t>
+  </si>
+  <si>
+    <t>Antsampanimahazo | Madagascar</t>
+  </si>
+  <si>
+    <t>Stage 4. Madagascar</t>
+  </si>
+  <si>
+    <t>Stage 7. Mallorca</t>
+  </si>
+  <si>
+    <t>Kato Gouves to Herakleion | Crete</t>
+  </si>
+  <si>
+    <t>Stage 3. Crete</t>
+  </si>
+  <si>
+    <t>Dambula to Lion Rock on Road | Sri Lanka</t>
+  </si>
+  <si>
+    <t>Stage 6. Sri Lanka</t>
+  </si>
+  <si>
+    <t>Stage 5. Calabria</t>
+  </si>
+  <si>
+    <t>Lago di Garda North West | Italy</t>
+  </si>
+  <si>
+    <t>Stage 1. Lago di Garda</t>
+  </si>
+  <si>
+    <t>Stage 2. Porto</t>
+  </si>
+  <si>
+    <t>Porto | Portugal</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Tu</t>
+  </si>
+  <si>
+    <t>We</t>
+  </si>
+  <si>
+    <t>Th</t>
+  </si>
+  <si>
+    <t>Time EST</t>
+  </si>
+  <si>
+    <t>Harrys TT Series Stage 1 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys TT Series Stage 2 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys TT Series Stage 3 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys TT Series Stage 4 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys TT Series Stage 5 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys TT Series Stage 6 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>9:30am</t>
+  </si>
+  <si>
+    <t>12:30PM</t>
+  </si>
+  <si>
+    <t>3:30PM</t>
+  </si>
+  <si>
+    <t>5:30PM</t>
   </si>
 </sst>
 </file>
@@ -158,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -169,6 +205,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,14 +518,14 @@
   <cols>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -500,68 +540,36 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>46235</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="3">
-        <v>46283</v>
+        <v>46334</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46235</v>
-      </c>
-      <c r="D3" s="3">
-        <v>46283</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3">
-        <v>46235</v>
-      </c>
-      <c r="D4" s="3">
-        <v>46283</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I9" s="4"/>
@@ -612,22 +620,22 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>46249</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="3">
-        <v>46255</v>
+        <v>46290</v>
       </c>
       <c r="E2" s="6">
-        <v>96466</v>
+        <v>96854</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -636,47 +644,50 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3">
-        <v>46256</v>
+        <v>46293</v>
       </c>
       <c r="D3" s="3">
-        <v>46262</v>
+        <v>46297</v>
       </c>
       <c r="E3" s="6">
-        <v>251360</v>
+        <v>251103</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>46263</v>
+        <v>46300</v>
       </c>
       <c r="D4" s="3">
-        <v>46269</v>
+        <v>46304</v>
       </c>
       <c r="E4" s="6">
-        <v>251436</v>
+        <v>96024</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3">
         <v>46270</v>
@@ -687,56 +698,68 @@
       <c r="E5" s="6">
         <v>96701</v>
       </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3">
-        <v>46277</v>
+        <v>46307</v>
       </c>
       <c r="D6" s="3">
-        <v>46283</v>
+        <v>46311</v>
       </c>
       <c r="E6" s="6">
-        <v>96854</v>
+        <v>250261</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46314</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46318</v>
+      </c>
+      <c r="E7" s="6">
+        <v>97043</v>
+      </c>
+      <c r="F7" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" s="3">
-        <v>46284</v>
-      </c>
-      <c r="D7" s="3">
-        <v>46290</v>
-      </c>
-      <c r="E7" s="6">
-        <v>251103</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46321</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46325</v>
+      </c>
+      <c r="E8" s="6">
+        <v>96479</v>
+      </c>
+      <c r="F8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46305</v>
-      </c>
-      <c r="D8" s="3">
-        <v>46252</v>
-      </c>
-      <c r="E8" s="6">
-        <v>96854</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -780,41 +803,1226 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="9"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>31</v>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="9">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8">
+        <v>46287</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="9">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="8">
+        <v>46287</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="9">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8">
+        <v>46287</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8">
+        <v>46287</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="9">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="8">
+        <v>46288</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="9">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="8">
+        <v>46288</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="9">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8">
+        <v>46288</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="8">
+        <v>46288</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="9">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="8">
+        <v>46289</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="9">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="8">
+        <v>46289</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="9">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="8">
+        <v>46289</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="9">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="8">
+        <v>46289</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="9">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="8">
+        <v>46294</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="9">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="8">
+        <v>46294</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="9">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="8">
+        <v>46294</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="9">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="8">
+        <v>46294</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="9">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="8">
+        <v>46295</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="9">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="8">
+        <v>46295</v>
+      </c>
+      <c r="E19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="9">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="8">
+        <v>46295</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="9">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="8">
+        <v>46295</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="9">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="8">
+        <v>46296</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="9">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="8">
+        <v>46296</v>
+      </c>
+      <c r="E23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="9">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="8">
+        <v>46296</v>
+      </c>
+      <c r="E24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="9">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="8">
+        <v>46296</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="9">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="8">
+        <v>46301</v>
+      </c>
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="9">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="8">
+        <v>46301</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="9">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="8">
+        <v>46301</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="9">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="8">
+        <v>46301</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="9">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="8">
+        <v>46302</v>
+      </c>
+      <c r="E30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="9">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="8">
+        <v>46302</v>
+      </c>
+      <c r="E31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="9">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="8">
+        <v>46302</v>
+      </c>
+      <c r="E32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="9">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="8">
+        <v>46302</v>
+      </c>
+      <c r="E33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="9">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="8">
+        <v>46303</v>
+      </c>
+      <c r="E34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="9">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="8">
+        <v>46303</v>
+      </c>
+      <c r="E35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="9">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="8">
+        <v>46303</v>
+      </c>
+      <c r="E36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="9">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="8">
+        <v>46303</v>
+      </c>
+      <c r="E37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="9">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="8">
+        <v>46308</v>
+      </c>
+      <c r="E38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="9">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="8">
+        <v>46308</v>
+      </c>
+      <c r="E39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="9">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="8">
+        <v>46308</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="9">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="8">
+        <v>46308</v>
+      </c>
+      <c r="E41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="9">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" s="8">
+        <v>46309</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="9">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="8">
+        <v>46309</v>
+      </c>
+      <c r="E43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44" s="9">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="8">
+        <v>46309</v>
+      </c>
+      <c r="E44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45" s="9">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="8">
+        <v>46309</v>
+      </c>
+      <c r="E45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46" s="9">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="8">
+        <v>46310</v>
+      </c>
+      <c r="E46" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47" s="9">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="8">
+        <v>46310</v>
+      </c>
+      <c r="E47" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="9">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="8">
+        <v>46310</v>
+      </c>
+      <c r="E48" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="9">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" s="8">
+        <v>46310</v>
+      </c>
+      <c r="E49" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="9">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="8">
+        <v>46315</v>
+      </c>
+      <c r="E50" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51" s="9">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="8">
+        <v>46315</v>
+      </c>
+      <c r="E51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="9">
+        <v>5</v>
+      </c>
+      <c r="C52" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="8">
+        <v>46315</v>
+      </c>
+      <c r="E52" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="9">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="8">
+        <v>46315</v>
+      </c>
+      <c r="E53" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B54" s="9">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="8">
+        <v>46316</v>
+      </c>
+      <c r="E54" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B55" s="9">
+        <v>5</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46316</v>
+      </c>
+      <c r="E55" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B56" s="9">
+        <v>5</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="8">
+        <v>46316</v>
+      </c>
+      <c r="E56" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B57" s="9">
+        <v>5</v>
+      </c>
+      <c r="C57" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="8">
+        <v>46316</v>
+      </c>
+      <c r="E57" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B58" s="9">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="8">
+        <v>46317</v>
+      </c>
+      <c r="E58" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="9">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="8">
+        <v>46317</v>
+      </c>
+      <c r="E59" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B60" s="9">
+        <v>5</v>
+      </c>
+      <c r="C60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="8">
+        <v>46317</v>
+      </c>
+      <c r="E60" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B61" s="9">
+        <v>5</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="8">
+        <v>46317</v>
+      </c>
+      <c r="E61" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B62" s="9">
+        <v>6</v>
+      </c>
+      <c r="C62" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" s="8">
+        <v>46322</v>
+      </c>
+      <c r="E62" t="s">
+        <v>40</v>
+      </c>
+      <c r="F62" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B63" s="9">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" s="8">
+        <v>46322</v>
+      </c>
+      <c r="E63" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B64" s="9">
+        <v>6</v>
+      </c>
+      <c r="C64" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="8">
+        <v>46322</v>
+      </c>
+      <c r="E64" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B65" s="9">
+        <v>6</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" s="8">
+        <v>46322</v>
+      </c>
+      <c r="E65" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B66" s="9">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="8">
+        <v>46323</v>
+      </c>
+      <c r="E66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B67" s="9">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67" s="8">
+        <v>46323</v>
+      </c>
+      <c r="E67" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B68" s="9">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>31</v>
+      </c>
+      <c r="D68" s="8">
+        <v>46323</v>
+      </c>
+      <c r="E68" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B69" s="9">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="8">
+        <v>46323</v>
+      </c>
+      <c r="E69" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B70" s="9">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>32</v>
+      </c>
+      <c r="D70" s="8">
+        <v>46324</v>
+      </c>
+      <c r="E70" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B71" s="9">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" s="8">
+        <v>46324</v>
+      </c>
+      <c r="E71" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B72" s="9">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" s="8">
+        <v>46324</v>
+      </c>
+      <c r="E72" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B73" s="9">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" s="8">
+        <v>46324</v>
+      </c>
+      <c r="E73" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B74" s="9">
+        <v>7</v>
+      </c>
+      <c r="C74" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="8">
+        <v>46329</v>
+      </c>
+      <c r="E74" t="s">
+        <v>40</v>
+      </c>
+      <c r="F74" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B75" s="9">
+        <v>7</v>
+      </c>
+      <c r="C75" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="8">
+        <v>46329</v>
+      </c>
+      <c r="E75" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B76" s="9">
+        <v>7</v>
+      </c>
+      <c r="C76" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="8">
+        <v>46329</v>
+      </c>
+      <c r="E76" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B77" s="9">
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" s="8">
+        <v>46329</v>
+      </c>
+      <c r="E77" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B78" s="9">
+        <v>7</v>
+      </c>
+      <c r="C78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D78" s="8">
+        <v>46330</v>
+      </c>
+      <c r="E78" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B79" s="9">
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" s="8">
+        <v>46330</v>
+      </c>
+      <c r="E79" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B80" s="9">
+        <v>7</v>
+      </c>
+      <c r="C80" t="s">
+        <v>31</v>
+      </c>
+      <c r="D80" s="8">
+        <v>46330</v>
+      </c>
+      <c r="E80" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B81" s="9">
+        <v>7</v>
+      </c>
+      <c r="C81" t="s">
+        <v>31</v>
+      </c>
+      <c r="D81" s="8">
+        <v>46330</v>
+      </c>
+      <c r="E81" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B82" s="9">
+        <v>7</v>
+      </c>
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E82" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B83" s="9">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>32</v>
+      </c>
+      <c r="D83" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E83" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B84" s="9">
+        <v>7</v>
+      </c>
+      <c r="C84" t="s">
+        <v>32</v>
+      </c>
+      <c r="D84" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E84" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B85" s="9">
+        <v>7</v>
+      </c>
+      <c r="C85" t="s">
+        <v>32</v>
+      </c>
+      <c r="D85" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E85" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="70">
   <si>
     <t>Name</t>
   </si>
@@ -120,24 +120,6 @@
     <t>Time EST</t>
   </si>
   <si>
-    <t>Harrys TT Series Stage 1 - harrysracing.ca</t>
-  </si>
-  <si>
-    <t>Harrys TT Series Stage 2 - harrysracing.ca</t>
-  </si>
-  <si>
-    <t>Harrys TT Series Stage 3 - harrysracing.ca</t>
-  </si>
-  <si>
-    <t>Harrys TT Series Stage 4 - harrysracing.ca</t>
-  </si>
-  <si>
-    <t>Harrys TT Series Stage 5 - harrysracing.ca</t>
-  </si>
-  <si>
-    <t>Harrys TT Series Stage 6 - harrysracing.ca</t>
-  </si>
-  <si>
     <t>9:30am</t>
   </si>
   <si>
@@ -148,6 +130,102 @@
   </si>
   <si>
     <t>5:30PM</t>
+  </si>
+  <si>
+    <t>Harrys Racing TT Series Stage 1 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys Racing TT Series Stage 3 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys Racing  TT Series Stage 2 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys Racing TT Series Stage 4 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys Racing TT Series Stage 5 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>HarrysRacing TT Series Stage 6 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>Harrys Racing TT Series Stage 6 - harrysracing.ca</t>
+  </si>
+  <si>
+    <t>35d060bd-589f-4e2d-8e93-fb8ebf8f35b1</t>
+  </si>
+  <si>
+    <t>b236efbc-5cac-4fd9-8513-b29630bee283</t>
+  </si>
+  <si>
+    <t>533c62a4-5edf-49ac-8f32-0d7247520e36</t>
+  </si>
+  <si>
+    <t>13215cfd-f237-481d-8fb2-c7a6ee95c85b</t>
+  </si>
+  <si>
+    <t>bc434d90-ec2e-4909-8ab5-7448c62029ec</t>
+  </si>
+  <si>
+    <t>896aaa12-9ec7-4dbe-a4a0-0ab9faadcd39</t>
+  </si>
+  <si>
+    <t>02f02625-529f-48fc-b396-223e3426ccc4</t>
+  </si>
+  <si>
+    <t>aa03e9e6-5e83-4446-bf2d-07e89fd8dd3a</t>
+  </si>
+  <si>
+    <t>5d38ca3e-690e-43a8-baaf-edc61e76f8b4</t>
+  </si>
+  <si>
+    <t>94ef1b2a-7018-4222-af8d-10bbf14136f6</t>
+  </si>
+  <si>
+    <t>0122beb3-d25d-45ca-8229-a5f09b7e8541</t>
+  </si>
+  <si>
+    <t>7a8e0ca2-2ddf-4672-b52f-dbd13b95fad4</t>
+  </si>
+  <si>
+    <t>efea7a99-523d-4d21-8894-6edb643a2915</t>
+  </si>
+  <si>
+    <t>f68598e3-b667-4218-9216-44623772041c</t>
+  </si>
+  <si>
+    <t>058a5925-1738-4e2b-b211-71d46e5746a9</t>
+  </si>
+  <si>
+    <t>401cccbf-eabb-43da-9ae5-84523cd82dff</t>
+  </si>
+  <si>
+    <t>Harrys Racing TT Series #1 Fall 2026</t>
+  </si>
+  <si>
+    <t>f59099d1-48b4-4a39-8b6f-0eaa860e92c7</t>
+  </si>
+  <si>
+    <t>4f118238-bb9f-4de1-8597-a10be32bccb2</t>
+  </si>
+  <si>
+    <t>7fc7705a-1570-45c0-be6f-8403ceb6ae67</t>
+  </si>
+  <si>
+    <t>70176470-bb98-4883-b085-1aba554816c2</t>
+  </si>
+  <si>
+    <t>e9429fa9-ea92-4156-8c6c-ed1be892242f</t>
+  </si>
+  <si>
+    <t>6a4c41ff-5d04-4699-90d4-aae0e071f348</t>
+  </si>
+  <si>
+    <t>a0b9995d-7c05-4344-bc87-4a99a7e3052c</t>
+  </si>
+  <si>
+    <t>b0d11bfa-203d-4476-8e52-81e6e6f7f892</t>
   </si>
 </sst>
 </file>
@@ -548,10 +626,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="C2" s="3">
-        <v>46286</v>
+        <v>46284</v>
       </c>
       <c r="D2" s="3">
         <v>46334</v>
@@ -593,7 +671,7 @@
   <cols>
     <col min="1" max="1" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
@@ -690,10 +768,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="3">
-        <v>46270</v>
+        <v>46307</v>
       </c>
       <c r="D5" s="3">
-        <v>46276</v>
+        <v>46311</v>
       </c>
       <c r="E5" s="6">
         <v>96701</v>
@@ -710,10 +788,10 @@
         <v>22</v>
       </c>
       <c r="C6" s="3">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="D6" s="3">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="E6" s="6">
         <v>250261</v>
@@ -730,10 +808,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="3">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="D7" s="3">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="E7" s="6">
         <v>97043</v>
@@ -750,10 +828,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="3">
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="D8" s="3">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="E8" s="6">
         <v>96479</v>
@@ -829,6 +907,9 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
       <c r="B2" s="9">
         <v>1</v>
       </c>
@@ -839,13 +920,16 @@
         <v>46287</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
       <c r="B3" s="9">
         <v>1</v>
       </c>
@@ -856,10 +940,13 @@
         <v>46287</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
       <c r="B4" s="9">
         <v>1</v>
       </c>
@@ -870,10 +957,13 @@
         <v>46287</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
       <c r="B5" s="9">
         <v>1</v>
       </c>
@@ -884,10 +974,13 @@
         <v>46287</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
       <c r="B6" s="9">
         <v>1</v>
       </c>
@@ -898,10 +991,13 @@
         <v>46288</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
       <c r="B7" s="9">
         <v>1</v>
       </c>
@@ -912,10 +1008,13 @@
         <v>46288</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
       <c r="B8" s="9">
         <v>1</v>
       </c>
@@ -926,10 +1025,13 @@
         <v>46288</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
       <c r="B9" s="9">
         <v>1</v>
       </c>
@@ -940,10 +1042,13 @@
         <v>46288</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
       <c r="B10" s="9">
         <v>1</v>
       </c>
@@ -954,10 +1059,13 @@
         <v>46289</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
       <c r="B11" s="9">
         <v>1</v>
       </c>
@@ -968,10 +1076,13 @@
         <v>46289</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
       <c r="B12" s="9">
         <v>1</v>
       </c>
@@ -982,10 +1093,13 @@
         <v>46289</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
       <c r="B13" s="9">
         <v>1</v>
       </c>
@@ -996,10 +1110,13 @@
         <v>46289</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
       <c r="B14" s="9">
         <v>2</v>
       </c>
@@ -1010,13 +1127,16 @@
         <v>46294</v>
       </c>
       <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" t="s">
         <v>40</v>
       </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
       <c r="B15" s="9">
         <v>2</v>
       </c>
@@ -1027,10 +1147,13 @@
         <v>46294</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
       <c r="B16" s="9">
         <v>2</v>
       </c>
@@ -1041,10 +1164,13 @@
         <v>46294</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
       <c r="B17" s="9">
         <v>2</v>
       </c>
@@ -1055,10 +1181,13 @@
         <v>46294</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
       <c r="B18" s="9">
         <v>2</v>
       </c>
@@ -1069,10 +1198,13 @@
         <v>46295</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
       <c r="B19" s="9">
         <v>2</v>
       </c>
@@ -1083,10 +1215,13 @@
         <v>46295</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
       <c r="B20" s="9">
         <v>2</v>
       </c>
@@ -1097,10 +1232,13 @@
         <v>46295</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
       <c r="B21" s="9">
         <v>2</v>
       </c>
@@ -1111,10 +1249,13 @@
         <v>46295</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
       <c r="B22" s="9">
         <v>2</v>
       </c>
@@ -1125,10 +1266,13 @@
         <v>46296</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
       <c r="B23" s="9">
         <v>2</v>
       </c>
@@ -1139,10 +1283,13 @@
         <v>46296</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
       <c r="B24" s="9">
         <v>2</v>
       </c>
@@ -1153,10 +1300,13 @@
         <v>46296</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
       <c r="B25" s="9">
         <v>2</v>
       </c>
@@ -1167,10 +1317,10 @@
         <v>46296</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B26" s="9">
         <v>3</v>
       </c>
@@ -1181,13 +1331,13 @@
         <v>46301</v>
       </c>
       <c r="E26" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="9">
         <v>3</v>
       </c>
@@ -1198,10 +1348,10 @@
         <v>46301</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="9">
         <v>3</v>
       </c>
@@ -1212,10 +1362,10 @@
         <v>46301</v>
       </c>
       <c r="E28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="9">
         <v>3</v>
       </c>
@@ -1226,10 +1376,10 @@
         <v>46301</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="9">
         <v>3</v>
       </c>
@@ -1240,10 +1390,10 @@
         <v>46302</v>
       </c>
       <c r="E30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="9">
         <v>3</v>
       </c>
@@ -1254,10 +1404,10 @@
         <v>46302</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="9">
         <v>3</v>
       </c>
@@ -1268,7 +1418,7 @@
         <v>46302</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
@@ -1282,7 +1432,7 @@
         <v>46302</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
@@ -1296,7 +1446,7 @@
         <v>46303</v>
       </c>
       <c r="E34" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
@@ -1310,7 +1460,7 @@
         <v>46303</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
@@ -1324,7 +1474,7 @@
         <v>46303</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
@@ -1338,7 +1488,7 @@
         <v>46303</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
@@ -1352,10 +1502,10 @@
         <v>46308</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
@@ -1369,7 +1519,7 @@
         <v>46308</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
@@ -1383,7 +1533,7 @@
         <v>46308</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
@@ -1397,7 +1547,7 @@
         <v>46308</v>
       </c>
       <c r="E41" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
@@ -1411,7 +1561,7 @@
         <v>46309</v>
       </c>
       <c r="E42" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
@@ -1425,7 +1575,7 @@
         <v>46309</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
@@ -1439,7 +1589,7 @@
         <v>46309</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
@@ -1453,7 +1603,7 @@
         <v>46309</v>
       </c>
       <c r="E45" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
@@ -1467,7 +1617,7 @@
         <v>46310</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
@@ -1481,7 +1631,7 @@
         <v>46310</v>
       </c>
       <c r="E47" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
@@ -1495,7 +1645,7 @@
         <v>46310</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
@@ -1509,7 +1659,7 @@
         <v>46310</v>
       </c>
       <c r="E49" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
@@ -1523,10 +1673,10 @@
         <v>46315</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F50" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
@@ -1540,7 +1690,7 @@
         <v>46315</v>
       </c>
       <c r="E51" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
@@ -1554,7 +1704,7 @@
         <v>46315</v>
       </c>
       <c r="E52" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
@@ -1568,7 +1718,7 @@
         <v>46315</v>
       </c>
       <c r="E53" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
@@ -1582,7 +1732,7 @@
         <v>46316</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
@@ -1596,7 +1746,7 @@
         <v>46316</v>
       </c>
       <c r="E55" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
@@ -1610,7 +1760,7 @@
         <v>46316</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
@@ -1624,7 +1774,7 @@
         <v>46316</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
@@ -1638,7 +1788,7 @@
         <v>46317</v>
       </c>
       <c r="E58" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
@@ -1652,7 +1802,7 @@
         <v>46317</v>
       </c>
       <c r="E59" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
@@ -1666,7 +1816,7 @@
         <v>46317</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
@@ -1680,7 +1830,7 @@
         <v>46317</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
@@ -1694,10 +1844,10 @@
         <v>46322</v>
       </c>
       <c r="E62" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
@@ -1711,7 +1861,7 @@
         <v>46322</v>
       </c>
       <c r="E63" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
@@ -1725,7 +1875,7 @@
         <v>46322</v>
       </c>
       <c r="E64" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
@@ -1739,7 +1889,7 @@
         <v>46322</v>
       </c>
       <c r="E65" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
@@ -1753,7 +1903,7 @@
         <v>46323</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
@@ -1767,7 +1917,7 @@
         <v>46323</v>
       </c>
       <c r="E67" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
@@ -1781,7 +1931,7 @@
         <v>46323</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
@@ -1795,7 +1945,7 @@
         <v>46323</v>
       </c>
       <c r="E69" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
@@ -1809,7 +1959,7 @@
         <v>46324</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
@@ -1823,7 +1973,7 @@
         <v>46324</v>
       </c>
       <c r="E71" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
@@ -1837,7 +1987,7 @@
         <v>46324</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
@@ -1851,7 +2001,7 @@
         <v>46324</v>
       </c>
       <c r="E73" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
@@ -1865,10 +2015,10 @@
         <v>46329</v>
       </c>
       <c r="E74" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F74" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
@@ -1882,7 +2032,7 @@
         <v>46329</v>
       </c>
       <c r="E75" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
@@ -1896,7 +2046,7 @@
         <v>46329</v>
       </c>
       <c r="E76" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
@@ -1910,7 +2060,7 @@
         <v>46329</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
@@ -1924,7 +2074,7 @@
         <v>46330</v>
       </c>
       <c r="E78" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
@@ -1938,7 +2088,7 @@
         <v>46330</v>
       </c>
       <c r="E79" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
@@ -1952,7 +2102,7 @@
         <v>46330</v>
       </c>
       <c r="E80" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
@@ -1966,7 +2116,7 @@
         <v>46330</v>
       </c>
       <c r="E81" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
@@ -1980,7 +2130,7 @@
         <v>46331</v>
       </c>
       <c r="E82" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
@@ -1994,7 +2144,7 @@
         <v>46331</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
@@ -2008,7 +2158,7 @@
         <v>46331</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
@@ -2022,7 +2172,7 @@
         <v>46331</v>
       </c>
       <c r="E85" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="69">
   <si>
     <t>Name</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>EventId</t>
-  </si>
-  <si>
-    <t>Harrys TT Series #1 Fall 2026</t>
   </si>
   <si>
     <t>Bagnara C. to Cannitello over Scilla - Calabria</t>
@@ -626,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="3">
         <v>46284</v>
@@ -698,10 +695,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3">
         <v>46286</v>
@@ -713,7 +710,7 @@
         <v>96854</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -722,10 +719,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3">
         <v>46293</v>
@@ -737,15 +734,15 @@
         <v>251103</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3">
         <v>46300</v>
@@ -757,15 +754,15 @@
         <v>96024</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3">
         <v>46307</v>
@@ -777,15 +774,15 @@
         <v>96701</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3">
         <v>46314</v>
@@ -797,15 +794,15 @@
         <v>250261</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3">
         <v>46321</v>
@@ -817,15 +814,15 @@
         <v>97043</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3">
         <v>46328</v>
@@ -837,7 +834,7 @@
         <v>96479</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -894,430 +891,430 @@
         <v>11</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s">
-        <v>28</v>
-      </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="9">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="8">
         <v>46287</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="9">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="8">
         <v>46287</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="8">
         <v>46287</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="9">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="8">
         <v>46287</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="9">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="8">
         <v>46288</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="9">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" s="8">
         <v>46288</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="9">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="8">
         <v>46288</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="8">
         <v>46288</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="9">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="8">
         <v>46289</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="9">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" s="8">
         <v>46289</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="9">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="8">
         <v>46289</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="9">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="8">
         <v>46289</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="9">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="8">
         <v>46294</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B15" s="9">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="8">
         <v>46294</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="9">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="8">
         <v>46294</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="9">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="8">
         <v>46294</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" s="9">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" s="8">
         <v>46295</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" s="9">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="8">
         <v>46295</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B20" s="9">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="8">
         <v>46295</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="9">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="8">
         <v>46295</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" s="9">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" s="8">
         <v>46296</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" s="9">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" s="8">
         <v>46296</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24" s="9">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" s="8">
         <v>46296</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B25" s="9">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" s="8">
         <v>46296</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1325,16 +1322,16 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="8">
         <v>46301</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1342,13 +1339,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" s="8">
         <v>46301</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1356,13 +1353,13 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="8">
         <v>46301</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1370,13 +1367,13 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="8">
         <v>46301</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1384,13 +1381,13 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" s="8">
         <v>46302</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1398,13 +1395,13 @@
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" s="8">
         <v>46302</v>
       </c>
       <c r="E31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1412,13 +1409,13 @@
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D32" s="8">
         <v>46302</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
@@ -1426,13 +1423,13 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D33" s="8">
         <v>46302</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
@@ -1440,13 +1437,13 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D34" s="8">
         <v>46303</v>
       </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
@@ -1454,13 +1451,13 @@
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D35" s="8">
         <v>46303</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
@@ -1468,13 +1465,13 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" s="8">
         <v>46303</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
@@ -1482,13 +1479,13 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" s="8">
         <v>46303</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
@@ -1496,16 +1493,16 @@
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" s="8">
         <v>46308</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
@@ -1513,13 +1510,13 @@
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" s="8">
         <v>46308</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
@@ -1527,13 +1524,13 @@
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D40" s="8">
         <v>46308</v>
       </c>
       <c r="E40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
@@ -1541,13 +1538,13 @@
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" s="8">
         <v>46308</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
@@ -1555,13 +1552,13 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D42" s="8">
         <v>46309</v>
       </c>
       <c r="E42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
@@ -1569,13 +1566,13 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D43" s="8">
         <v>46309</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
@@ -1583,13 +1580,13 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D44" s="8">
         <v>46309</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
@@ -1597,13 +1594,13 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D45" s="8">
         <v>46309</v>
       </c>
       <c r="E45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
@@ -1611,13 +1608,13 @@
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D46" s="8">
         <v>46310</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
@@ -1625,13 +1622,13 @@
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" s="8">
         <v>46310</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
@@ -1639,13 +1636,13 @@
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D48" s="8">
         <v>46310</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
@@ -1653,13 +1650,13 @@
         <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D49" s="8">
         <v>46310</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
@@ -1667,16 +1664,16 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D50" s="8">
         <v>46315</v>
       </c>
       <c r="E50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
@@ -1684,13 +1681,13 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D51" s="8">
         <v>46315</v>
       </c>
       <c r="E51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
@@ -1698,13 +1695,13 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D52" s="8">
         <v>46315</v>
       </c>
       <c r="E52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
@@ -1712,13 +1709,13 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D53" s="8">
         <v>46315</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
@@ -1726,13 +1723,13 @@
         <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54" s="8">
         <v>46316</v>
       </c>
       <c r="E54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
@@ -1740,13 +1737,13 @@
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D55" s="8">
         <v>46316</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
@@ -1754,13 +1751,13 @@
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D56" s="8">
         <v>46316</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
@@ -1768,13 +1765,13 @@
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D57" s="8">
         <v>46316</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
@@ -1782,13 +1779,13 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D58" s="8">
         <v>46317</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
@@ -1796,13 +1793,13 @@
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D59" s="8">
         <v>46317</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
@@ -1810,13 +1807,13 @@
         <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D60" s="8">
         <v>46317</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
@@ -1824,13 +1821,13 @@
         <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D61" s="8">
         <v>46317</v>
       </c>
       <c r="E61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
@@ -1838,16 +1835,16 @@
         <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D62" s="8">
         <v>46322</v>
       </c>
       <c r="E62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
@@ -1855,13 +1852,13 @@
         <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D63" s="8">
         <v>46322</v>
       </c>
       <c r="E63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
@@ -1869,13 +1866,13 @@
         <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D64" s="8">
         <v>46322</v>
       </c>
       <c r="E64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
@@ -1883,13 +1880,13 @@
         <v>6</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D65" s="8">
         <v>46322</v>
       </c>
       <c r="E65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
@@ -1897,13 +1894,13 @@
         <v>6</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66" s="8">
         <v>46323</v>
       </c>
       <c r="E66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
@@ -1911,13 +1908,13 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D67" s="8">
         <v>46323</v>
       </c>
       <c r="E67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
@@ -1925,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="C68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D68" s="8">
         <v>46323</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
@@ -1939,13 +1936,13 @@
         <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D69" s="8">
         <v>46323</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
@@ -1953,13 +1950,13 @@
         <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D70" s="8">
         <v>46324</v>
       </c>
       <c r="E70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
@@ -1967,13 +1964,13 @@
         <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D71" s="8">
         <v>46324</v>
       </c>
       <c r="E71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
@@ -1981,13 +1978,13 @@
         <v>6</v>
       </c>
       <c r="C72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D72" s="8">
         <v>46324</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
@@ -1995,13 +1992,13 @@
         <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D73" s="8">
         <v>46324</v>
       </c>
       <c r="E73" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
@@ -2009,16 +2006,16 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D74" s="8">
         <v>46329</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
@@ -2026,13 +2023,13 @@
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D75" s="8">
         <v>46329</v>
       </c>
       <c r="E75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
@@ -2040,13 +2037,13 @@
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D76" s="8">
         <v>46329</v>
       </c>
       <c r="E76" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
@@ -2054,13 +2051,13 @@
         <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D77" s="8">
         <v>46329</v>
       </c>
       <c r="E77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
@@ -2068,13 +2065,13 @@
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D78" s="8">
         <v>46330</v>
       </c>
       <c r="E78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
@@ -2082,13 +2079,13 @@
         <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D79" s="8">
         <v>46330</v>
       </c>
       <c r="E79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
@@ -2096,13 +2093,13 @@
         <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D80" s="8">
         <v>46330</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
@@ -2110,13 +2107,13 @@
         <v>7</v>
       </c>
       <c r="C81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D81" s="8">
         <v>46330</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
@@ -2124,13 +2121,13 @@
         <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D82" s="8">
         <v>46331</v>
       </c>
       <c r="E82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
@@ -2138,13 +2135,13 @@
         <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D83" s="8">
         <v>46331</v>
       </c>
       <c r="E83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
@@ -2152,13 +2149,13 @@
         <v>7</v>
       </c>
       <c r="C84" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D84" s="8">
         <v>46331</v>
       </c>
       <c r="E84" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
@@ -2166,13 +2163,13 @@
         <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D85" s="8">
         <v>46331</v>
       </c>
       <c r="E85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="81">
   <si>
     <t>Name</t>
   </si>
@@ -223,6 +223,42 @@
   </si>
   <si>
     <t>b0d11bfa-203d-4476-8e52-81e6e6f7f892</t>
+  </si>
+  <si>
+    <t>d8d904b7-bc01-47dc-93db-6499d135845c</t>
+  </si>
+  <si>
+    <t>fdaf0ea4-bf6a-4345-a13d-69d58b0d7b91</t>
+  </si>
+  <si>
+    <t>0b4c15ce-b78e-43cf-acf2-715c08c775b6</t>
+  </si>
+  <si>
+    <t>d280be3d-7f19-4716-9636-421aa1dd6b38</t>
+  </si>
+  <si>
+    <t>f42705c7-fd5a-417f-aac9-f4ba97c3cd02</t>
+  </si>
+  <si>
+    <t>9645f765-8d51-4094-904e-b44d651dca38</t>
+  </si>
+  <si>
+    <t>17419660-fb7e-46e0-aeef-55d6a05991ef</t>
+  </si>
+  <si>
+    <t>b8a99ae9-4025-4153-b664-cd643828e424</t>
+  </si>
+  <si>
+    <t>8d35c7f8-bc86-449a-8e4e-be380fc72a8c</t>
+  </si>
+  <si>
+    <t>18c22b40-661e-4a73-abcf-0d72c7159f46</t>
+  </si>
+  <si>
+    <t>6cd4d99a-d82b-4937-8fc7-40dc8b46b7eb</t>
+  </si>
+  <si>
+    <t>b2f307a9-b83e-4d1b-bf45-567080e5b2b8</t>
   </si>
 </sst>
 </file>
@@ -1318,6 +1354,9 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
       <c r="B26" s="9">
         <v>3</v>
       </c>
@@ -1335,6 +1374,9 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
       <c r="B27" s="9">
         <v>3</v>
       </c>
@@ -1349,6 +1391,9 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
       <c r="B28" s="9">
         <v>3</v>
       </c>
@@ -1363,6 +1408,9 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>72</v>
+      </c>
       <c r="B29" s="9">
         <v>3</v>
       </c>
@@ -1377,6 +1425,9 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>73</v>
+      </c>
       <c r="B30" s="9">
         <v>3</v>
       </c>
@@ -1391,6 +1442,9 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>74</v>
+      </c>
       <c r="B31" s="9">
         <v>3</v>
       </c>
@@ -1405,6 +1459,9 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>75</v>
+      </c>
       <c r="B32" s="9">
         <v>3</v>
       </c>
@@ -1418,7 +1475,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>76</v>
+      </c>
       <c r="B33" s="9">
         <v>3</v>
       </c>
@@ -1432,7 +1492,10 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>77</v>
+      </c>
       <c r="B34" s="9">
         <v>3</v>
       </c>
@@ -1446,7 +1509,10 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
       <c r="B35" s="9">
         <v>3</v>
       </c>
@@ -1460,7 +1526,10 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>79</v>
+      </c>
       <c r="B36" s="9">
         <v>3</v>
       </c>
@@ -1474,7 +1543,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>80</v>
+      </c>
       <c r="B37" s="9">
         <v>3</v>
       </c>
@@ -1488,7 +1560,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B38" s="9">
         <v>4</v>
       </c>
@@ -1505,7 +1577,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B39" s="9">
         <v>4</v>
       </c>
@@ -1519,7 +1591,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B40" s="9">
         <v>4</v>
       </c>
@@ -1533,7 +1605,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B41" s="9">
         <v>4</v>
       </c>
@@ -1547,7 +1619,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B42" s="9">
         <v>4</v>
       </c>
@@ -1561,7 +1633,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B43" s="9">
         <v>4</v>
       </c>
@@ -1575,7 +1647,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B44" s="9">
         <v>4</v>
       </c>
@@ -1589,7 +1661,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B45" s="9">
         <v>4</v>
       </c>
@@ -1603,7 +1675,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B46" s="9">
         <v>4</v>
       </c>
@@ -1617,7 +1689,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B47" s="9">
         <v>4</v>
       </c>
@@ -1631,7 +1703,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B48" s="9">
         <v>4</v>
       </c>

--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="83">
   <si>
     <t>Name</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t>b2f307a9-b83e-4d1b-bf45-567080e5b2b8</t>
+  </si>
+  <si>
+    <t>10:00PM</t>
+  </si>
+  <si>
+    <t>a021ba2b-1d78-4da0-bfe0-296e980f204f</t>
   </si>
 </sst>
 </file>
@@ -914,7 +920,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.77734375" bestFit="1" customWidth="1"/>
@@ -1148,27 +1154,24 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B14" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="8">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="9">
         <v>2</v>
@@ -1180,12 +1183,15 @@
         <v>46294</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="9">
         <v>2</v>
@@ -1197,12 +1203,12 @@
         <v>46294</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" s="9">
         <v>2</v>
@@ -1214,29 +1220,29 @@
         <v>46294</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B18" s="9">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="8">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="9">
         <v>2</v>
@@ -1248,12 +1254,12 @@
         <v>46295</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="9">
         <v>2</v>
@@ -1265,12 +1271,12 @@
         <v>46295</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" s="9">
         <v>2</v>
@@ -1282,29 +1288,29 @@
         <v>46295</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" s="9">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" s="8">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="9">
         <v>2</v>
@@ -1316,12 +1322,12 @@
         <v>46296</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B24" s="9">
         <v>2</v>
@@ -1333,12 +1339,12 @@
         <v>46296</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B25" s="9">
         <v>2</v>
@@ -1350,32 +1356,29 @@
         <v>46296</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B26" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D26" s="8">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
-      </c>
-      <c r="F26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" s="9">
         <v>3</v>
@@ -1387,12 +1390,15 @@
         <v>46301</v>
       </c>
       <c r="E27" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="F27" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B28" s="9">
         <v>3</v>
@@ -1404,12 +1410,12 @@
         <v>46301</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B29" s="9">
         <v>3</v>
@@ -1421,29 +1427,29 @@
         <v>46301</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30" s="9">
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="8">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" s="9">
         <v>3</v>
@@ -1455,12 +1461,12 @@
         <v>46302</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B32" s="9">
         <v>3</v>
@@ -1472,12 +1478,12 @@
         <v>46302</v>
       </c>
       <c r="E32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" s="9">
         <v>3</v>
@@ -1489,29 +1495,29 @@
         <v>46302</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B34" s="9">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D34" s="8">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B35" s="9">
         <v>3</v>
@@ -1523,12 +1529,12 @@
         <v>46303</v>
       </c>
       <c r="E35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B36" s="9">
         <v>3</v>
@@ -1540,12 +1546,12 @@
         <v>46303</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B37" s="9">
         <v>3</v>
@@ -1557,24 +1563,24 @@
         <v>46303</v>
       </c>
       <c r="E37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="9">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="8">
+        <v>46303</v>
+      </c>
+      <c r="E38" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="9">
-        <v>4</v>
-      </c>
-      <c r="C38" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="8">
-        <v>46308</v>
-      </c>
-      <c r="E38" t="s">
-        <v>33</v>
-      </c>
-      <c r="F38" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1588,7 +1594,10 @@
         <v>46308</v>
       </c>
       <c r="E39" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="F39" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -1602,7 +1611,7 @@
         <v>46308</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1616,7 +1625,7 @@
         <v>46308</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1624,13 +1633,13 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D42" s="8">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1644,7 +1653,7 @@
         <v>46309</v>
       </c>
       <c r="E43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1658,7 +1667,7 @@
         <v>46309</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1672,7 +1681,7 @@
         <v>46309</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1680,13 +1689,13 @@
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D46" s="8">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -1700,7 +1709,7 @@
         <v>46310</v>
       </c>
       <c r="E47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -1714,7 +1723,7 @@
         <v>46310</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
@@ -1728,24 +1737,21 @@
         <v>46310</v>
       </c>
       <c r="E49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D50" s="8">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
-      </c>
-      <c r="F50" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
@@ -1759,7 +1765,10 @@
         <v>46315</v>
       </c>
       <c r="E51" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="F51" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
@@ -1773,7 +1782,7 @@
         <v>46315</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
@@ -1787,7 +1796,7 @@
         <v>46315</v>
       </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
@@ -1795,13 +1804,13 @@
         <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D54" s="8">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
@@ -1815,7 +1824,7 @@
         <v>46316</v>
       </c>
       <c r="E55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
@@ -1829,7 +1838,7 @@
         <v>46316</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
@@ -1843,7 +1852,7 @@
         <v>46316</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
@@ -1851,13 +1860,13 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D58" s="8">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
@@ -1871,7 +1880,7 @@
         <v>46317</v>
       </c>
       <c r="E59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
@@ -1885,7 +1894,7 @@
         <v>46317</v>
       </c>
       <c r="E60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
@@ -1899,24 +1908,21 @@
         <v>46317</v>
       </c>
       <c r="E61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D62" s="8">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="E62" t="s">
-        <v>33</v>
-      </c>
-      <c r="F62" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
@@ -1930,7 +1936,10 @@
         <v>46322</v>
       </c>
       <c r="E63" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="F63" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
@@ -1944,7 +1953,7 @@
         <v>46322</v>
       </c>
       <c r="E64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
@@ -1958,7 +1967,7 @@
         <v>46322</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
@@ -1966,13 +1975,13 @@
         <v>6</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D66" s="8">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E66" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
@@ -1986,7 +1995,7 @@
         <v>46323</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
@@ -2000,7 +2009,7 @@
         <v>46323</v>
       </c>
       <c r="E68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
@@ -2014,7 +2023,7 @@
         <v>46323</v>
       </c>
       <c r="E69" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
@@ -2022,13 +2031,13 @@
         <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D70" s="8">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="E70" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
@@ -2042,7 +2051,7 @@
         <v>46324</v>
       </c>
       <c r="E71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
@@ -2056,7 +2065,7 @@
         <v>46324</v>
       </c>
       <c r="E72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
@@ -2070,24 +2079,21 @@
         <v>46324</v>
       </c>
       <c r="E73" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B74" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D74" s="8">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="E74" t="s">
-        <v>33</v>
-      </c>
-      <c r="F74" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
@@ -2101,7 +2107,10 @@
         <v>46329</v>
       </c>
       <c r="E75" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="F75" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
@@ -2115,7 +2124,7 @@
         <v>46329</v>
       </c>
       <c r="E76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
@@ -2129,7 +2138,7 @@
         <v>46329</v>
       </c>
       <c r="E77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
@@ -2137,13 +2146,13 @@
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D78" s="8">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="E78" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
@@ -2157,7 +2166,7 @@
         <v>46330</v>
       </c>
       <c r="E79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
@@ -2171,7 +2180,7 @@
         <v>46330</v>
       </c>
       <c r="E80" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
@@ -2185,7 +2194,7 @@
         <v>46330</v>
       </c>
       <c r="E81" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
@@ -2193,13 +2202,13 @@
         <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D82" s="8">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="E82" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
@@ -2213,7 +2222,7 @@
         <v>46331</v>
       </c>
       <c r="E83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
@@ -2227,7 +2236,7 @@
         <v>46331</v>
       </c>
       <c r="E84" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
@@ -2241,6 +2250,20 @@
         <v>46331</v>
       </c>
       <c r="E85" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B86" s="9">
+        <v>7</v>
+      </c>
+      <c r="C86" t="s">
+        <v>31</v>
+      </c>
+      <c r="D86" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E86" t="s">
         <v>36</v>
       </c>
     </row>

--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="86">
   <si>
     <t>Name</t>
   </si>
@@ -261,10 +261,19 @@
     <t>b2f307a9-b83e-4d1b-bf45-567080e5b2b8</t>
   </si>
   <si>
+    <t>10:00pm</t>
+  </si>
+  <si>
     <t>10:00PM</t>
   </si>
   <si>
     <t>a021ba2b-1d78-4da0-bfe0-296e980f204f</t>
+  </si>
+  <si>
+    <t>558581f2-61de-482d-8775-28c0a0a705e1</t>
+  </si>
+  <si>
+    <t>95da701b-925e-4601-8001-2440e419b211</t>
   </si>
 </sst>
 </file>
@@ -920,7 +929,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.77734375" bestFit="1" customWidth="1"/>
@@ -1154,7 +1163,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14" s="9">
         <v>1</v>
@@ -1166,7 +1175,7 @@
         <v>46289</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1242,24 +1251,24 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="8">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="9">
         <v>2</v>
@@ -1271,12 +1280,12 @@
         <v>46295</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B21" s="9">
         <v>2</v>
@@ -1288,12 +1297,12 @@
         <v>46295</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22" s="9">
         <v>2</v>
@@ -1305,29 +1314,29 @@
         <v>46295</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B23" s="9">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="8">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="9">
         <v>2</v>
@@ -1339,12 +1348,12 @@
         <v>46296</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="9">
         <v>2</v>
@@ -1356,12 +1365,12 @@
         <v>46296</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B26" s="9">
         <v>2</v>
@@ -1373,49 +1382,46 @@
         <v>46296</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B27" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D27" s="8">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
-      </c>
-      <c r="F27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B28" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28" s="8">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="E28" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B29" s="9">
         <v>3</v>
@@ -1427,12 +1433,15 @@
         <v>46301</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B30" s="9">
         <v>3</v>
@@ -1444,46 +1453,46 @@
         <v>46301</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" s="9">
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="8">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B32" s="9">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="8">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="E32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B33" s="9">
         <v>3</v>
@@ -1495,12 +1504,12 @@
         <v>46302</v>
       </c>
       <c r="E33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B34" s="9">
         <v>3</v>
@@ -1512,46 +1521,46 @@
         <v>46302</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B35" s="9">
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" s="8">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B36" s="9">
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36" s="8">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="E36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B37" s="9">
         <v>3</v>
@@ -1563,12 +1572,12 @@
         <v>46303</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B38" s="9">
         <v>3</v>
@@ -1580,38 +1589,41 @@
         <v>46303</v>
       </c>
       <c r="E38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="9">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="8">
+        <v>46303</v>
+      </c>
+      <c r="E39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="9">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="8">
+        <v>46303</v>
+      </c>
+      <c r="E40" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="9">
-        <v>4</v>
-      </c>
-      <c r="C39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="8">
-        <v>46308</v>
-      </c>
-      <c r="E39" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="9">
-        <v>4</v>
-      </c>
-      <c r="C40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="8">
-        <v>46308</v>
-      </c>
-      <c r="E40" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1625,7 +1637,10 @@
         <v>46308</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F41" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1639,7 +1654,7 @@
         <v>46308</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1647,13 +1662,13 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D43" s="8">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1661,13 +1676,13 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" s="8">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E44" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1681,7 +1696,7 @@
         <v>46309</v>
       </c>
       <c r="E45" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1695,7 +1710,7 @@
         <v>46309</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -1703,13 +1718,13 @@
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D47" s="8">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -1717,13 +1732,13 @@
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D48" s="8">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
@@ -1737,7 +1752,7 @@
         <v>46310</v>
       </c>
       <c r="E49" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
@@ -1751,38 +1766,35 @@
         <v>46310</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D51" s="8">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
-      </c>
-      <c r="F51" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D52" s="8">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
@@ -1796,7 +1808,10 @@
         <v>46315</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F53" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
@@ -1810,7 +1825,7 @@
         <v>46315</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
@@ -1818,13 +1833,13 @@
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D55" s="8">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="E55" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
@@ -1832,13 +1847,13 @@
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D56" s="8">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="E56" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
@@ -1852,7 +1867,7 @@
         <v>46316</v>
       </c>
       <c r="E57" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
@@ -1866,7 +1881,7 @@
         <v>46316</v>
       </c>
       <c r="E58" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
@@ -1874,13 +1889,13 @@
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D59" s="8">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
@@ -1888,13 +1903,13 @@
         <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D60" s="8">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="E60" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
@@ -1908,7 +1923,7 @@
         <v>46317</v>
       </c>
       <c r="E61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
@@ -1922,38 +1937,35 @@
         <v>46317</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D63" s="8">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="E63" t="s">
-        <v>33</v>
-      </c>
-      <c r="F63" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D64" s="8">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="E64" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
@@ -1967,7 +1979,10 @@
         <v>46322</v>
       </c>
       <c r="E65" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F65" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
@@ -1981,7 +1996,7 @@
         <v>46322</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
@@ -1989,13 +2004,13 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D67" s="8">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
@@ -2003,13 +2018,13 @@
         <v>6</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D68" s="8">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E68" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
@@ -2023,7 +2038,7 @@
         <v>46323</v>
       </c>
       <c r="E69" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
@@ -2037,7 +2052,7 @@
         <v>46323</v>
       </c>
       <c r="E70" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
@@ -2045,13 +2060,13 @@
         <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D71" s="8">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
@@ -2059,13 +2074,13 @@
         <v>6</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D72" s="8">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
@@ -2079,7 +2094,7 @@
         <v>46324</v>
       </c>
       <c r="E73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
@@ -2093,38 +2108,35 @@
         <v>46324</v>
       </c>
       <c r="E74" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B75" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D75" s="8">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="E75" t="s">
-        <v>33</v>
-      </c>
-      <c r="F75" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C76" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D76" s="8">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
@@ -2138,7 +2150,10 @@
         <v>46329</v>
       </c>
       <c r="E77" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F77" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
@@ -2152,7 +2167,7 @@
         <v>46329</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
@@ -2160,13 +2175,13 @@
         <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D79" s="8">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="E79" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
@@ -2174,13 +2189,13 @@
         <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D80" s="8">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="E80" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
@@ -2194,7 +2209,7 @@
         <v>46330</v>
       </c>
       <c r="E81" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
@@ -2208,7 +2223,7 @@
         <v>46330</v>
       </c>
       <c r="E82" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
@@ -2216,13 +2231,13 @@
         <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D83" s="8">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="E83" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
@@ -2230,13 +2245,13 @@
         <v>7</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D84" s="8">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="E84" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
@@ -2250,7 +2265,7 @@
         <v>46331</v>
       </c>
       <c r="E85" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
@@ -2264,6 +2279,34 @@
         <v>46331</v>
       </c>
       <c r="E86" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B87" s="9">
+        <v>7</v>
+      </c>
+      <c r="C87" t="s">
+        <v>31</v>
+      </c>
+      <c r="D87" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E87" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B88" s="9">
+        <v>7</v>
+      </c>
+      <c r="C88" t="s">
+        <v>31</v>
+      </c>
+      <c r="D88" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E88" t="s">
         <v>36</v>
       </c>
     </row>

--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
     <sheet name="Stages" sheetId="2" r:id="rId2"/>
     <sheet name="Races" sheetId="3" r:id="rId3"/>
+    <sheet name="community" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="89">
   <si>
     <t>Name</t>
   </si>
@@ -274,6 +275,15 @@
   </si>
   <si>
     <t>95da701b-925e-4601-8001-2440e419b211</t>
+  </si>
+  <si>
+    <t>52298c21-d570-4e4c-b162-997822baef64</t>
+  </si>
+  <si>
+    <t>49ebc53c-910a-45f9-b3ff-8fe8587b1a5a</t>
+  </si>
+  <si>
+    <t>https://riders.rouvy.com/social/communities/bf28346e-e6fc-4e35-b7d4-0a43b950c96a</t>
   </si>
 </sst>
 </file>
@@ -929,7 +939,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.77734375" bestFit="1" customWidth="1"/>
@@ -1492,24 +1502,24 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B33" s="9">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D33" s="8">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" s="9">
         <v>3</v>
@@ -1521,12 +1531,12 @@
         <v>46302</v>
       </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B35" s="9">
         <v>3</v>
@@ -1538,12 +1548,12 @@
         <v>46302</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" s="9">
         <v>3</v>
@@ -1555,29 +1565,29 @@
         <v>46302</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" s="9">
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" s="8">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="E37" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B38" s="9">
         <v>3</v>
@@ -1589,12 +1599,12 @@
         <v>46303</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B39" s="9">
         <v>3</v>
@@ -1606,12 +1616,12 @@
         <v>46303</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B40" s="9">
         <v>3</v>
@@ -1623,38 +1633,41 @@
         <v>46303</v>
       </c>
       <c r="E40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="9">
+        <v>3</v>
+      </c>
+      <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="8">
+        <v>46303</v>
+      </c>
+      <c r="E41" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="9">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="8">
-        <v>46308</v>
-      </c>
-      <c r="E41" t="s">
-        <v>33</v>
-      </c>
-      <c r="F41" t="s">
-        <v>40</v>
-      </c>
-    </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>87</v>
+      </c>
       <c r="B42" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D42" s="8">
-        <v>46308</v>
+        <v>46303</v>
       </c>
       <c r="E42" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1668,7 +1681,10 @@
         <v>46308</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F43" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1682,7 +1698,7 @@
         <v>46308</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1690,13 +1706,13 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D45" s="8">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E45" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1704,13 +1720,13 @@
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D46" s="8">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -1724,7 +1740,7 @@
         <v>46309</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -1738,7 +1754,7 @@
         <v>46309</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
@@ -1746,13 +1762,13 @@
         <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D49" s="8">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
@@ -1760,13 +1776,13 @@
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D50" s="8">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="E50" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
@@ -1780,7 +1796,7 @@
         <v>46310</v>
       </c>
       <c r="E51" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
@@ -1794,38 +1810,35 @@
         <v>46310</v>
       </c>
       <c r="E52" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D53" s="8">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
-      </c>
-      <c r="F53" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D54" s="8">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="E54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
@@ -1839,7 +1852,10 @@
         <v>46315</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F55" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
@@ -1853,7 +1869,7 @@
         <v>46315</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
@@ -1861,13 +1877,13 @@
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D57" s="8">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="E57" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
@@ -1875,13 +1891,13 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D58" s="8">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
@@ -1895,7 +1911,7 @@
         <v>46316</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
@@ -1909,7 +1925,7 @@
         <v>46316</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
@@ -1917,13 +1933,13 @@
         <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D61" s="8">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
@@ -1931,13 +1947,13 @@
         <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D62" s="8">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="E62" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
@@ -1951,7 +1967,7 @@
         <v>46317</v>
       </c>
       <c r="E63" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
@@ -1965,38 +1981,35 @@
         <v>46317</v>
       </c>
       <c r="E64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D65" s="8">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
-      </c>
-      <c r="F65" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D66" s="8">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="E66" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
@@ -2010,7 +2023,10 @@
         <v>46322</v>
       </c>
       <c r="E67" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F67" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
@@ -2024,7 +2040,7 @@
         <v>46322</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
@@ -2032,13 +2048,13 @@
         <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D69" s="8">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E69" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
@@ -2046,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D70" s="8">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E70" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
@@ -2066,7 +2082,7 @@
         <v>46323</v>
       </c>
       <c r="E71" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
@@ -2080,7 +2096,7 @@
         <v>46323</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
@@ -2088,13 +2104,13 @@
         <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D73" s="8">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="E73" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
@@ -2102,13 +2118,13 @@
         <v>6</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D74" s="8">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
@@ -2122,7 +2138,7 @@
         <v>46324</v>
       </c>
       <c r="E75" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
@@ -2136,38 +2152,35 @@
         <v>46324</v>
       </c>
       <c r="E76" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D77" s="8">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="E77" t="s">
-        <v>33</v>
-      </c>
-      <c r="F77" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D78" s="8">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="E78" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
@@ -2181,7 +2194,10 @@
         <v>46329</v>
       </c>
       <c r="E79" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F79" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
@@ -2195,7 +2211,7 @@
         <v>46329</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
@@ -2203,13 +2219,13 @@
         <v>7</v>
       </c>
       <c r="C81" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D81" s="8">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="E81" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.3">
@@ -2217,13 +2233,13 @@
         <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D82" s="8">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="E82" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.3">
@@ -2237,7 +2253,7 @@
         <v>46330</v>
       </c>
       <c r="E83" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.3">
@@ -2251,7 +2267,7 @@
         <v>46330</v>
       </c>
       <c r="E84" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
@@ -2259,13 +2275,13 @@
         <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D85" s="8">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="E85" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
@@ -2273,13 +2289,13 @@
         <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D86" s="8">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="E86" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
@@ -2293,7 +2309,7 @@
         <v>46331</v>
       </c>
       <c r="E87" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.3">
@@ -2307,7 +2323,50 @@
         <v>46331</v>
       </c>
       <c r="E88" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B89" s="9">
+        <v>7</v>
+      </c>
+      <c r="C89" t="s">
+        <v>31</v>
+      </c>
+      <c r="D89" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E89" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B90" s="9">
+        <v>7</v>
+      </c>
+      <c r="C90" t="s">
+        <v>31</v>
+      </c>
+      <c r="D90" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E90" t="s">
         <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="103">
   <si>
     <t>Name</t>
   </si>
@@ -284,6 +284,48 @@
   </si>
   <si>
     <t>https://riders.rouvy.com/social/communities/bf28346e-e6fc-4e35-b7d4-0a43b950c96a</t>
+  </si>
+  <si>
+    <t>aac27817-4819-45df-8c79-da1d0f04e9ad</t>
+  </si>
+  <si>
+    <t>637cc281-19b0-48d1-8eb6-f54f95ddc552</t>
+  </si>
+  <si>
+    <t>7de00311-672a-433e-a3f7-8d2b8ae45919</t>
+  </si>
+  <si>
+    <t>e49abcf8-6074-448c-b530-fa68f8b64cd1</t>
+  </si>
+  <si>
+    <t>522a182b-861b-4070-8665-8a8f07349dc9</t>
+  </si>
+  <si>
+    <t>6396cbd4-d81e-43ff-9638-5a54f30af79c</t>
+  </si>
+  <si>
+    <t>af71abb5-3610-4185-a5e8-4d3ab0b60081</t>
+  </si>
+  <si>
+    <t>f67bd35a-9d1c-41ff-a404-d5e78c09f1de</t>
+  </si>
+  <si>
+    <t>22e8bfd3-2b83-4f40-acec-4c57dbb5af8c</t>
+  </si>
+  <si>
+    <t>bf89e7be-b231-472b-bda9-1c90e8373b48</t>
+  </si>
+  <si>
+    <t>f666b64b-5c9d-46ab-b9bf-7da95b39ed79</t>
+  </si>
+  <si>
+    <t>c4434133-dbd8-485c-8b7c-d9f99f7a89ae</t>
+  </si>
+  <si>
+    <t>2a90861b-95d8-465d-aa68-ffba2f353260</t>
+  </si>
+  <si>
+    <t>80ea2193-0429-4b57-b71e-e8e78f424926</t>
   </si>
 </sst>
 </file>
@@ -939,7 +981,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.77734375" bestFit="1" customWidth="1"/>
@@ -1671,6 +1713,9 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>89</v>
+      </c>
       <c r="B43" s="9">
         <v>4</v>
       </c>
@@ -1688,6 +1733,9 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>90</v>
+      </c>
       <c r="B44" s="9">
         <v>4</v>
       </c>
@@ -1702,6 +1750,9 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>91</v>
+      </c>
       <c r="B45" s="9">
         <v>4</v>
       </c>
@@ -1716,6 +1767,9 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>92</v>
+      </c>
       <c r="B46" s="9">
         <v>4</v>
       </c>
@@ -1730,20 +1784,26 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>93</v>
+      </c>
       <c r="B47" s="9">
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D47" s="8">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E47" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
       <c r="B48" s="9">
         <v>4</v>
       </c>
@@ -1754,10 +1814,13 @@
         <v>46309</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>95</v>
+      </c>
       <c r="B49" s="9">
         <v>4</v>
       </c>
@@ -1768,10 +1831,13 @@
         <v>46309</v>
       </c>
       <c r="E49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>96</v>
+      </c>
       <c r="B50" s="9">
         <v>4</v>
       </c>
@@ -1782,24 +1848,30 @@
         <v>46309</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>97</v>
+      </c>
       <c r="B51" s="9">
         <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D51" s="8">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>98</v>
+      </c>
       <c r="B52" s="9">
         <v>4</v>
       </c>
@@ -1810,10 +1882,13 @@
         <v>46310</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>99</v>
+      </c>
       <c r="B53" s="9">
         <v>4</v>
       </c>
@@ -1824,10 +1899,13 @@
         <v>46310</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>100</v>
+      </c>
       <c r="B54" s="9">
         <v>4</v>
       </c>
@@ -1838,41 +1916,44 @@
         <v>46310</v>
       </c>
       <c r="E54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" s="9">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46310</v>
+      </c>
+      <c r="E55" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="9">
-        <v>5</v>
-      </c>
-      <c r="C55" t="s">
-        <v>29</v>
-      </c>
-      <c r="D55" s="8">
-        <v>46315</v>
-      </c>
-      <c r="E55" t="s">
-        <v>33</v>
-      </c>
-      <c r="F55" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>102</v>
+      </c>
       <c r="B56" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D56" s="8">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="E56" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B57" s="9">
         <v>5</v>
       </c>
@@ -1883,10 +1964,13 @@
         <v>46315</v>
       </c>
       <c r="E57" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="F57" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B58" s="9">
         <v>5</v>
       </c>
@@ -1897,38 +1981,38 @@
         <v>46315</v>
       </c>
       <c r="E58" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B59" s="9">
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D59" s="8">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="E59" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B60" s="9">
         <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D60" s="8">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="E60" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B61" s="9">
         <v>5</v>
       </c>
@@ -1939,10 +2023,10 @@
         <v>46316</v>
       </c>
       <c r="E61" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B62" s="9">
         <v>5</v>
       </c>
@@ -1953,35 +2037,35 @@
         <v>46316</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B63" s="9">
         <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D63" s="8">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="E63" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B64" s="9">
         <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D64" s="8">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="E64" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
@@ -1995,7 +2079,7 @@
         <v>46317</v>
       </c>
       <c r="E65" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
@@ -2009,38 +2093,35 @@
         <v>46317</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D67" s="8">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
-      </c>
-      <c r="F67" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B68" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D68" s="8">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="E68" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
@@ -2054,7 +2135,10 @@
         <v>46322</v>
       </c>
       <c r="E69" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F69" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
@@ -2068,7 +2152,7 @@
         <v>46322</v>
       </c>
       <c r="E70" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
@@ -2076,13 +2160,13 @@
         <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D71" s="8">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
@@ -2090,13 +2174,13 @@
         <v>6</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D72" s="8">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
@@ -2110,7 +2194,7 @@
         <v>46323</v>
       </c>
       <c r="E73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
@@ -2124,7 +2208,7 @@
         <v>46323</v>
       </c>
       <c r="E74" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
@@ -2132,13 +2216,13 @@
         <v>6</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D75" s="8">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="E75" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
@@ -2146,13 +2230,13 @@
         <v>6</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D76" s="8">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
@@ -2166,7 +2250,7 @@
         <v>46324</v>
       </c>
       <c r="E77" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
@@ -2180,41 +2264,38 @@
         <v>46324</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D79" s="8">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="E79" t="s">
-        <v>33</v>
-      </c>
-      <c r="F79" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D80" s="8">
-        <v>46329</v>
+        <v>46324</v>
       </c>
       <c r="E80" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="9">
         <v>7</v>
       </c>
@@ -2225,10 +2306,13 @@
         <v>46329</v>
       </c>
       <c r="E81" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="F81" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="9">
         <v>7</v>
       </c>
@@ -2239,38 +2323,38 @@
         <v>46329</v>
       </c>
       <c r="E82" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="9">
         <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D83" s="8">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="E83" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" s="9">
         <v>7</v>
       </c>
       <c r="C84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D84" s="8">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="E84" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="9">
         <v>7</v>
       </c>
@@ -2281,10 +2365,10 @@
         <v>46330</v>
       </c>
       <c r="E85" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="9">
         <v>7</v>
       </c>
@@ -2295,38 +2379,38 @@
         <v>46330</v>
       </c>
       <c r="E86" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="9">
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D87" s="8">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="E87" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="9">
         <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D88" s="8">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="E88" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="9">
         <v>7</v>
       </c>
@@ -2337,10 +2421,10 @@
         <v>46331</v>
       </c>
       <c r="E89" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="9">
         <v>7</v>
       </c>
@@ -2351,6 +2435,34 @@
         <v>46331</v>
       </c>
       <c r="E90" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B91" s="9">
+        <v>7</v>
+      </c>
+      <c r="C91" t="s">
+        <v>31</v>
+      </c>
+      <c r="D91" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E91" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B92" s="9">
+        <v>7</v>
+      </c>
+      <c r="C92" t="s">
+        <v>31</v>
+      </c>
+      <c r="D92" s="8">
+        <v>46331</v>
+      </c>
+      <c r="E92" t="s">
         <v>36</v>
       </c>
     </row>

--- a/database/series_setup.xlsx
+++ b/database/series_setup.xlsx
@@ -148,9 +148,6 @@
     <t>HarrysRacing TT Series Stage 6 - harrysracing.ca</t>
   </si>
   <si>
-    <t>Harrys Racing TT Series Stage 6 - harrysracing.ca</t>
-  </si>
-  <si>
     <t>35d060bd-589f-4e2d-8e93-fb8ebf8f35b1</t>
   </si>
   <si>
@@ -326,6 +323,9 @@
   </si>
   <si>
     <t>80ea2193-0429-4b57-b71e-e8e78f424926</t>
+  </si>
+  <si>
+    <t>Harrys Racing TT Series Stage 7 - harrysracing.ca</t>
   </si>
 </sst>
 </file>
@@ -726,7 +726,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3">
         <v>46284</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -822,7 +822,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -862,7 +862,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="9">
         <v>1</v>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="9">
         <v>1</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="9">
         <v>1</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="9">
         <v>1</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="9">
         <v>1</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="9">
         <v>1</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="9">
         <v>1</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="9">
         <v>1</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="9">
         <v>1</v>
@@ -1181,7 +1181,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="9">
         <v>1</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="9">
         <v>1</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B14" s="9">
         <v>1</v>
@@ -1227,12 +1227,12 @@
         <v>46289</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="9">
         <v>2</v>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="9">
         <v>2</v>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="9">
         <v>2</v>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="9">
         <v>2</v>
@@ -1303,7 +1303,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>2</v>
@@ -1315,12 +1315,12 @@
         <v>46294</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20" s="9">
         <v>2</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="9">
         <v>2</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22" s="9">
         <v>2</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" s="9">
         <v>2</v>
@@ -1388,7 +1388,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B24" s="9">
         <v>2</v>
@@ -1405,7 +1405,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" s="9">
         <v>2</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="9">
         <v>2</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" s="9">
         <v>2</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B28" s="9">
         <v>2</v>
@@ -1468,12 +1468,12 @@
         <v>46296</v>
       </c>
       <c r="E28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B29" s="9">
         <v>3</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="9">
         <v>3</v>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B31" s="9">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B32" s="9">
         <v>3</v>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="9">
         <v>3</v>
@@ -1556,12 +1556,12 @@
         <v>46301</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B34" s="9">
         <v>3</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" s="9">
         <v>3</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B36" s="9">
         <v>3</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" s="9">
         <v>3</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B38" s="9">
         <v>3</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B39" s="9">
         <v>3</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B40" s="9">
         <v>3</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B41" s="9">
         <v>3</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B42" s="9">
         <v>3</v>
@@ -1709,12 +1709,12 @@
         <v>46303</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" s="9">
         <v>4</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B44" s="9">
         <v>4</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B45" s="9">
         <v>4</v>
@@ -1768,7 +1768,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46" s="9">
         <v>4</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="9">
         <v>4</v>
@@ -1797,12 +1797,12 @@
         <v>46308</v>
       </c>
       <c r="E47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" s="9">
         <v>4</v>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" s="9">
         <v>4</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B50" s="9">
         <v>4</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="9">
         <v>4</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="9">
         <v>4</v>
@@ -1887,7 +1887,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" s="9">
         <v>4</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B54" s="9">
         <v>4</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B55" s="9">
         <v>4</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B56" s="9">
         <v>4</v>
@@ -1950,7 +1950,7 @@
         <v>46310</v>
       </c>
       <c r="E56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2309,7 +2309,7 @@
         <v>33</v>
       </c>
       <c r="F81" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
@@ -2478,7 +2478,7 @@
   <sheetData>
     <row r="3" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
